--- a/datos/coordinador.xlsx
+++ b/datos/coordinador.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alex Varela\Pictures\JULIO\AGOSTO\Página KPIS\KPI-s-CAR\datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E98C9E5-3FD9-434D-9146-1A5F89E8AA5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F80FE0E4-4F5F-4E64-8A05-3232BFB4D8DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="75">
   <si>
     <t>SEGUIMIENTO MENSUAL – CHECKLIST DE CUMPLIMIENTO</t>
   </si>
@@ -92,81 +92,27 @@
     <t>COORDINACIÓN DE CUADRILLAS ELÉCTRICAS</t>
   </si>
   <si>
-    <t>100% actualizado</t>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
-    <t>100% de movimientos registrados</t>
-  </si>
-  <si>
-    <t>Atención de averías, emergencias, mantenimientos y trabajos programados</t>
-  </si>
-  <si>
-    <t>100% de eventos atendidos y registrados</t>
-  </si>
-  <si>
-    <t>100% de trabajos programados con responsable, fecha y recursos definidos</t>
-  </si>
-  <si>
     <t>Registro y coordinación de maniobras, desconexiones y restablecimientos conforme a procedimiento</t>
   </si>
   <si>
-    <t>100% de maniobras ejecutadas bajo procedimiento</t>
-  </si>
-  <si>
-    <t>100% de paros requeridos gestionados y comunicados</t>
-  </si>
-  <si>
-    <t>Verificar que los trabajos se ejecuten con procedimientos de seguridad</t>
-  </si>
-  <si>
-    <t>100% de trabajos verificados conforme al procedimiento de seguridad</t>
-  </si>
-  <si>
-    <t>Dar seguimiento al avance de trabajo y verificar la calidad del trabajo realizado</t>
-  </si>
-  <si>
-    <t>100% de trabajos con seguimiento y calidad verificada</t>
-  </si>
-  <si>
-    <t>Control de combustible</t>
-  </si>
-  <si>
     <t>PCB’s</t>
   </si>
   <si>
-    <t>100% de casos identificados con seguimiento</t>
-  </si>
-  <si>
     <t>Fauna</t>
   </si>
   <si>
-    <t>100% de eventos registrados y atendidos</t>
-  </si>
-  <si>
-    <t>100% de casos registrados y gestionados</t>
-  </si>
-  <si>
     <t>Identificación y reporte de faltantes o desviaciones de materiales requeridos</t>
   </si>
   <si>
-    <t>100% de desviaciones identificadas y reportadas</t>
-  </si>
-  <si>
     <t>Leonardo Arrieta Carranza</t>
   </si>
   <si>
-    <t>100% de consumos registrados; desviaciones identificadas y justificadas.</t>
-  </si>
-  <si>
     <t>Registro actualizado de cambios físicos y activos incorporados o modificados en la red y proyectos</t>
   </si>
   <si>
-    <t>Control del mantenimiento de móviles</t>
-  </si>
-  <si>
     <t>Coordinación de la unidad de derrama</t>
   </si>
   <si>
@@ -179,24 +125,12 @@
     <t>Control de materiales retirados, utilizados y devueltos por cada cuadrilla, sin perdida de activos.</t>
   </si>
   <si>
-    <t>Programación Semanal de los trabajos de cuadrilla para el cumplimiento de objetivos</t>
-  </si>
-  <si>
     <t>Presentar la programación mensual de trabajos, responsables, recursos y prioridades por cuadrilla</t>
   </si>
   <si>
-    <t xml:space="preserve">Gestionar maniobras, desconexiones y restablecimiento de servicios con los procedimientos establecidos </t>
-  </si>
-  <si>
-    <t>Control de proyectos: ejecución</t>
-  </si>
-  <si>
     <t>% de consumo de combustible mensual registrado por movil</t>
   </si>
   <si>
-    <t xml:space="preserve">Control de desviaciones en disponibilidad de materiales (Stock mínimo) </t>
-  </si>
-  <si>
     <t>Control y registro de equipos o materiales asociados a PCB y cierre con éxito de la campaña</t>
   </si>
   <si>
@@ -206,15 +140,9 @@
     <t>Registro y seguimiento de los trabajos de la unidad de derrama</t>
   </si>
   <si>
-    <t>100% actualizado y sin desviaciones</t>
-  </si>
-  <si>
     <t xml:space="preserve">Verificación del estado, Deckra, Mantenimiento y Reportes a la jefatura para la ejecución de mantenimientos </t>
   </si>
   <si>
-    <t>≥ 85% atendidas y 100% registradas</t>
-  </si>
-  <si>
     <t>Registro y coordinación oportuna de averías, emergencias, mantenimientos y trabajos programados en Ordenes de trabajo</t>
   </si>
   <si>
@@ -230,31 +158,106 @@
     <t>Seguimiento de la ejecución de proyectos, hacer cierre y control de los mismos.</t>
   </si>
   <si>
-    <t>100% de los proyectos cerrados registrados</t>
-  </si>
-  <si>
-    <t>Reportar los cambios en la red e inversión al encargado del GIS</t>
-  </si>
-  <si>
-    <t>100% de cambios de red e inversión registrados en GIS</t>
-  </si>
-  <si>
-    <t>Control mensual de inventario de herramienta personal - herramienta de móvil</t>
-  </si>
-  <si>
-    <t>Seguimiento de órdenes de trabajo del departamento eléctrico en CRM</t>
-  </si>
-  <si>
     <t>Seguimiento del estado, avance y cierre de las órdenes de trabajo asignadas en CRM conforme proceso.</t>
   </si>
   <si>
     <t>Verificación del estado, mantenimiento de la herramientas, reposiciones y reportes de perdidas</t>
   </si>
   <si>
-    <t>Coordinación de materiales para cuadrillas (retiro de bodega, devolución a bodega y control de utilización de materiales)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gestionar los paros programados y comunicar los requeridos por trabajos cotidianos </t>
+    <t>100% de permisos, vacaciones y ausencias conocidos registrados en el control de personal, con fecha y autorización correspondiente.</t>
+  </si>
+  <si>
+    <t>100% de móviles con revisión mensual documentada del estado, vencimientos y necesidades de mantenimiento; anomalías reportadas a jefatura.</t>
+  </si>
+  <si>
+    <t>Mantenimiento de móviles</t>
+  </si>
+  <si>
+    <t>Inventario de herramientas</t>
+  </si>
+  <si>
+    <t>100% de inventarios programados ejecutados y documentados, con faltantes, daños y necesidades de reposición reportados.</t>
+  </si>
+  <si>
+    <t>Control de materiales (retiro, devolución y control cruzado con bodega)</t>
+  </si>
+  <si>
+    <t>100% de retiros y devoluciones respaldados en boletas; y documentadas por entrega de proyecto o bien en OT de averia.</t>
+  </si>
+  <si>
+    <t>Órdenes de trabajo CRM</t>
+  </si>
+  <si>
+    <t>Al menos 85% de órdenes asignadas atendidas dentro del plazo definido y 100% con estado actualizado y evidencia de gestión.</t>
+  </si>
+  <si>
+    <t>Averías y emergencias</t>
+  </si>
+  <si>
+    <t>100% de eventos recibidos registrados y canalizados conforme a prioridad y procedimiento, con fecha, responsable y seguimiento.</t>
+  </si>
+  <si>
+    <t>Programación semanal</t>
+  </si>
+  <si>
+    <t>100% de programaciones semanales entregadas antes del inicio de la semana, con trabajos, prioridades, responsables y recursos.</t>
+  </si>
+  <si>
+    <t>Maniobras eléctricas</t>
+  </si>
+  <si>
+    <t>100% de maniobras coordinadas con autorización, registro y verificación documental del procedimiento aplicable.</t>
+  </si>
+  <si>
+    <t>Paros programados</t>
+  </si>
+  <si>
+    <t>100% de paros bajo su coordinación con autorización y comunicación documentadas dentro de los plazos establecidos.</t>
+  </si>
+  <si>
+    <t>Seguridad laboral</t>
+  </si>
+  <si>
+    <t>100% de inspecciones de seguridad programadas realizadas, documentadas y con incumplimientos comunicados para su corrección.</t>
+  </si>
+  <si>
+    <t>Calidad de trabajos</t>
+  </si>
+  <si>
+    <t>100% de órdenes cerradas sujetas al control de calidad definido, con revisión documentada y reporte de hallazgos.</t>
+  </si>
+  <si>
+    <t>Control de proyectos</t>
+  </si>
+  <si>
+    <t>100% de proyectos asignados con avance mensual actualizado, pendientes identificados y cierre documentado cuando corresponda.</t>
+  </si>
+  <si>
+    <t>Actualización GIS</t>
+  </si>
+  <si>
+    <t>100% de cambios de red reportados al encargado GIS mediante registro con ubicación, descripción y fecha, dentro del plazo de 4 días trans el cierre.</t>
+  </si>
+  <si>
+    <t>Combustible</t>
+  </si>
+  <si>
+    <t>100% de consumos registrados por móvil y revisión mensual de variaciones con justificación de diferencias detectadas.</t>
+  </si>
+  <si>
+    <t>Existencias mínimas de stock por mantenimiento</t>
+  </si>
+  <si>
+    <t>100% de faltantes detectados en las revisiones programadas reportados a bodega y jefatura, con seguimiento documentado.</t>
+  </si>
+  <si>
+    <t>100% de casos asignados con registro, estado y seguimiento actualizado; acciones ejecutadas respaldadas documentalmente.</t>
+  </si>
+  <si>
+    <t>100% de eventos reportados registrados, clasificados y gestionados conforme al procedimiento establecido.</t>
+  </si>
+  <si>
+    <t>100% de trabajos asignados con programación, seguimiento de ejecución y estado de cierre documentados.</t>
   </si>
 </sst>
 </file>
@@ -425,7 +428,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -438,9 +441,6 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -514,6 +514,15 @@
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="15" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -877,70 +886,70 @@
   <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.5546875" style="9" customWidth="1"/>
+    <col min="1" max="1" width="5.5546875" style="8" customWidth="1"/>
     <col min="2" max="2" width="72.109375" customWidth="1"/>
     <col min="3" max="3" width="104.6640625" customWidth="1"/>
-    <col min="4" max="4" width="48.109375" customWidth="1"/>
-    <col min="5" max="5" width="10.6640625" style="7" customWidth="1"/>
-    <col min="6" max="6" width="9.77734375" style="7" customWidth="1"/>
+    <col min="4" max="4" width="48.109375" style="30" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" style="6" customWidth="1"/>
+    <col min="6" max="6" width="9.77734375" style="6" customWidth="1"/>
     <col min="7" max="7" width="34.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.3">
-      <c r="A1" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
+      <c r="A1" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
+      <c r="A2" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
     </row>
     <row r="3" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="26">
+      <c r="B3" s="25">
         <v>46316</v>
       </c>
-      <c r="C3" s="27"/>
-      <c r="D3" s="5" t="s">
+      <c r="C3" s="26"/>
+      <c r="D3" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="28" t="s">
-        <v>40</v>
-      </c>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
+      <c r="E3" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" s="27"/>
+      <c r="G3" s="27"/>
     </row>
     <row r="4" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="29">
+      <c r="B4" s="28">
         <v>46325</v>
       </c>
-      <c r="C4" s="27"/>
-      <c r="D4" s="5" t="s">
+      <c r="C4" s="26"/>
+      <c r="D4" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="28" t="s">
+      <c r="E4" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
     </row>
     <row r="5" spans="1:7" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
@@ -955,10 +964,10 @@
       <c r="D5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="9" t="s">
         <v>10</v>
       </c>
       <c r="G5" s="2" t="s">
@@ -966,437 +975,437 @@
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="21"/>
-      <c r="C6" s="21"/>
-      <c r="D6" s="21"/>
-      <c r="E6" s="21"/>
-      <c r="F6" s="21"/>
-      <c r="G6" s="21"/>
-    </row>
-    <row r="7" spans="1:7" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="13">
-        <v>1</v>
-      </c>
-      <c r="B7" s="14" t="s">
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+    </row>
+    <row r="7" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="12">
+        <v>1</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="F7" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="G7" s="17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="45.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="12">
+        <v>2</v>
+      </c>
+      <c r="B8" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C8" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="F8" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" s="17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="12">
+        <v>3</v>
+      </c>
+      <c r="B9" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="C9" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="E9" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="F9" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" s="17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="12">
+        <v>4</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="E10" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="F10" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" s="17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="45.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="12">
+        <v>5</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="F11" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11" s="17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="12">
+        <v>6</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="F12" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12" s="17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="12">
+        <v>8</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="E13" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="F13" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" s="17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="44.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="12">
+        <v>9</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="E7" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="F7" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="G7" s="18" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="13">
-        <v>2</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="C8" s="15" t="s">
+      <c r="E14" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="F14" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14" s="17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="44.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="12">
+        <v>10</v>
+      </c>
+      <c r="B15" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="D8" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="E8" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="F8" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="G8" s="18" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="13">
-        <v>3</v>
-      </c>
-      <c r="B9" s="14" t="s">
+      <c r="C15" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="E15" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="F15" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15" s="17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="12">
+        <v>11</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="E16" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="F16" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16" s="17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="43.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="12">
+        <v>12</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="E17" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="F17" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="G17" s="17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="12">
+        <v>13</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="E18" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="F18" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18" s="17"/>
+    </row>
+    <row r="19" spans="1:7" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="12">
+        <v>14</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="E19" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="F19" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" s="17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="12">
+        <v>15</v>
+      </c>
+      <c r="B20" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C20" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="D20" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="E20" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="F20" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" s="17"/>
+    </row>
+    <row r="21" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="12">
+        <v>16</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D21" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="D9" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="F9" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="G9" s="18" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="13">
-        <v>4</v>
-      </c>
-      <c r="B10" s="14" t="s">
+      <c r="E21" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="F21" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" s="17"/>
+    </row>
+    <row r="22" spans="1:7" s="5" customFormat="1" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="12">
+        <v>17</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="C10" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="D10" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="F10" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="G10" s="18" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="13">
-        <v>5</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="D11" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="E11" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="F11" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="G11" s="18" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="13">
-        <v>6</v>
-      </c>
-      <c r="B12" s="14" t="s">
+      <c r="E22" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="F22" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" s="19" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" s="5" customFormat="1" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="12">
+        <v>18</v>
+      </c>
+      <c r="B23" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="D12" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="F12" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="G12" s="18" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="13">
-        <v>8</v>
-      </c>
-      <c r="B13" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="C13" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="D13" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="E13" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="F13" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="G13" s="18" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="13">
-        <v>9</v>
-      </c>
-      <c r="B14" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="C14" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="D14" s="16" t="s">
+      <c r="C23" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="D23" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="E23" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="F23" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" s="19" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" s="5" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="12">
+        <v>19</v>
+      </c>
+      <c r="B24" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="E14" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="F14" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="G14" s="18" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="13">
-        <v>10</v>
-      </c>
-      <c r="B15" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="C15" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="D15" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="E15" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="F15" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="G15" s="18" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="13">
-        <v>11</v>
-      </c>
-      <c r="B16" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="C16" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="D16" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="E16" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="F16" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="G16" s="18" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="13">
+      <c r="C24" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="D24" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="E24" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="F24" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" s="19" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="B17" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C17" s="15" t="s">
-        <v>63</v>
-      </c>
-      <c r="D17" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="E17" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="F17" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="G17" s="18" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="13">
-        <v>13</v>
-      </c>
-      <c r="B18" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="C18" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="D18" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="E18" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="F18" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="G18" s="18"/>
-    </row>
-    <row r="19" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="13">
-        <v>14</v>
-      </c>
-      <c r="B19" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="C19" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="D19" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="E19" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="F19" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="G19" s="18" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="13">
-        <v>15</v>
-      </c>
-      <c r="B20" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="C20" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="D20" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="E20" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="F20" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="G20" s="18"/>
-    </row>
-    <row r="21" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="13">
-        <v>16</v>
-      </c>
-      <c r="B21" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="C21" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="D21" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="E21" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="F21" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="G21" s="18"/>
-    </row>
-    <row r="22" spans="1:7" s="6" customFormat="1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="13">
-        <v>17</v>
-      </c>
-      <c r="B22" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C22" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="D22" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="E22" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="F22" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="G22" s="20" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" s="6" customFormat="1" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="13">
-        <v>18</v>
-      </c>
-      <c r="B23" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="C23" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="D23" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="E23" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="F23" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="G23" s="20" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" s="6" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="13">
-        <v>19</v>
-      </c>
-      <c r="B24" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="C24" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="D24" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="E24" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="F24" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="G24" s="20" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="B25" s="23"/>
-      <c r="C25" s="23"/>
-      <c r="D25" s="23"/>
-      <c r="E25" s="11">
+      <c r="B25" s="22"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="10">
         <f>IFERROR(COUNTIFS(E7:E24,TRUE,F7:F24,FALSE)/COUNTIF(F7:F24,FALSE),0)</f>
         <v>1</v>
       </c>
-      <c r="F25" s="23"/>
-      <c r="G25" s="23"/>
+      <c r="F25" s="22"/>
+      <c r="G25" s="22"/>
     </row>
     <row r="27" spans="1:7" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="4">
@@ -1405,7 +1414,7 @@
       </c>
     </row>
     <row r="28" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="9" t="s">
+      <c r="A28" s="8" t="s">
         <v>17</v>
       </c>
       <c r="B28" s="3">
@@ -1415,14 +1424,14 @@
       <c r="C28" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D28" s="3">
+      <c r="D28" s="31">
         <f>COUNTIFS(E7:E24,FALSE,F7:F24,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="E28" s="12" t="s">
+      <c r="E28" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="F28" s="7">
+      <c r="F28" s="6">
         <f>COUNTIF(F7:F24,TRUE)</f>
         <v>0</v>
       </c>
